--- a/employee_surveys/027_role_specific_training_needs_survey--employee_surveys.xlsx
+++ b/employee_surveys/027_role_specific_training_needs_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -888,17 +888,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>skills_assessed_choices</t>
+          <t>training_topics_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Adaptability</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>leadership/management</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Leadership/Management</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>leadership/management</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Leadership/Management</t>
+          <t>Presentation</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Presentation</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>project_management</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Data Analysis</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>data_analysis</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Data Analysis</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>problem_solving</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Problem Solving</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -1029,29 +1029,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>goal_setting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Goal Setting</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>training_topics_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>goal_setting</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>semi-annual</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
     </row>
@@ -1131,27 +1131,10 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>semi-annual</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Semi-Annual</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>training_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>annually</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Annually</t>
         </is>
